--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487463_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487463_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7586</v>
+        <v>2.7513</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4884</v>
+        <v>2.5723</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2702</v>
+        <v>0.179</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.9544</v>
+        <v>-0.5122</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8843</v>
+        <v>0.1742</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.8387</v>
+        <v>-0.6863</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1883</v>
+        <v>1.3462</v>
       </c>
       <c r="K2" t="n">
-        <v>1.628</v>
+        <v>0.5783</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4397</v>
+        <v>0.7679</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.1427</v>
+        <v>-1.8583</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7437</v>
+        <v>-0.4041</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.399</v>
+        <v>-1.4542</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9377</v>
+        <v>0.3917</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3917</v>
+        <v>-2.3502</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3294</v>
+        <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3848</v>
+        <v>-0.7781</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6919</v>
+        <v>-0.0735</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3071</v>
+        <v>-0.7046</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3905</v>
+        <v>3.6498</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.6498</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4918</v>
+        <v>2.1958</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2059</v>
+        <v>1.7652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2859</v>
+        <v>0.4306</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5122</v>
+        <v>-1.9544</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1742</v>
+        <v>0.8843</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6863</v>
+        <v>-2.8387</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3462</v>
+        <v>1.1883</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5783</v>
+        <v>1.628</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7679</v>
+        <v>-0.4397</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8583</v>
+        <v>-3.1427</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4041</v>
+        <v>-0.7437</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4542</v>
+        <v>-2.399</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3917</v>
+        <v>2.9377</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3502</v>
+        <v>-0.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7419</v>
+        <v>3.3294</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0376</v>
+        <v>0.8219</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4399</v>
+        <v>0.9687</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5977</v>
+        <v>-0.1467</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6498</v>
+        <v>0.3905</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6498</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6241</v>
+        <v>1.829</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9503</v>
+        <v>2.1285</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3262</v>
+        <v>-0.2994</v>
       </c>
       <c r="G4" t="n">
         <v>1.5626</v>
@@ -766,13 +766,13 @@
         <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.101</v>
+        <v>0.104</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0223</v>
+        <v>0.2005</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1233</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>2.7086</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="G5" t="n">
         <v>0.2729</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2551</v>
+        <v>-0.2283</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2551</v>
+        <v>-0.2283</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.373</v>
+        <v>-0.1357</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.229</v>
+        <v>0.0351</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.144</v>
+        <v>-0.1708</v>
       </c>
       <c r="G6" t="n">
         <v>-0.181</v>
@@ -922,13 +922,13 @@
         <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3084</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1782</v>
+        <v>0.0859</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1302</v>
+        <v>-0.1569</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2754</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3158</v>
+        <v>-1.2891</v>
       </c>
       <c r="E7" t="n">
         <v>-1.0576</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2582</v>
+        <v>-0.2315</v>
       </c>
       <c r="G7" t="n">
         <v>-0.295</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0416</v>
+        <v>-0.0149</v>
       </c>
       <c r="T7" t="n">
         <v>0.077</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LOPE REBOLLO</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0681</v>
+        <v>-1.5153</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8055</v>
+        <v>-0.919</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2626</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7541</v>
+        <v>0.1137</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3223</v>
+        <v>0.0881</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0764</v>
+        <v>0.0256</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4875</v>
+        <v>1.046</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7962</v>
+        <v>0.3589</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2836</v>
+        <v>0.6871</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2667</v>
+        <v>-0.9323</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4739</v>
+        <v>-0.2708</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7927</v>
+        <v>-0.6615</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5098</v>
+        <v>-0.258</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3388</v>
+        <v>-0.0065</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.171</v>
+        <v>-0.2516</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>S. LOPE REBOLLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.183</v>
+        <v>-2.0073</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5065</v>
+        <v>-1.5843</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6765</v>
+        <v>-0.423</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1137</v>
+        <v>-1.7541</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0881</v>
+        <v>0.3223</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0256</v>
+        <v>-2.0764</v>
       </c>
       <c r="J9" t="n">
-        <v>1.046</v>
+        <v>-0.4875</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3589</v>
+        <v>0.7962</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6871</v>
+        <v>-1.2836</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9323</v>
+        <v>-1.2667</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2708</v>
+        <v>-0.4739</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6615</v>
+        <v>-0.7927</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9258</v>
+        <v>-0.449</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.594</v>
+        <v>-0.1176</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3318</v>
+        <v>-0.3314</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2287</v>
+        <v>-2.831</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0098</v>
+        <v>-2.7457</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.219</v>
+        <v>-0.0853</v>
       </c>
       <c r="G10" t="n">
         <v>2.1443</v>
@@ -1234,13 +1234,13 @@
         <v>2.7419</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.789</v>
+        <v>-0.3913</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1076</v>
+        <v>0.1564</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6814</v>
+        <v>-0.5477</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2754</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0936</v>
+        <v>-3.7328</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3401</v>
+        <v>-3.0596</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7534</v>
+        <v>-0.6732</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7346</v>
@@ -1312,13 +1312,13 @@
         <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5341</v>
+        <v>-0.1734</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0371</v>
+        <v>0.2435</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.497</v>
+        <v>-0.4168</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5789</v>
+        <v>-5.0702</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4733</v>
+        <v>-3.7241</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1056</v>
+        <v>-1.3461</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0163</v>
@@ -1390,13 +1390,13 @@
         <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6997</v>
+        <v>-0.191</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7193000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0196</v>
+        <v>-0.221</v>
       </c>
       <c r="V12" t="n">
         <v>-1.492</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.9488</v>
+        <v>-9.7607</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.7772</v>
+        <v>-6.5892</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1716</v>
+        <v>-3.1714</v>
       </c>
       <c r="G13" t="n">
         <v>-6.3541</v>
@@ -1468,13 +1468,13 @@
         <v>17.6262</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8173</v>
+        <v>-1.6291</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3762999999999999</v>
+        <v>1.5644</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.1936</v>
+        <v>-3.1935</v>
       </c>
       <c r="V13" t="n">
         <v>4.0978</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.426</v>
+        <v>5.9666</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6181</v>
+        <v>4.7761</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8078</v>
+        <v>1.1905</v>
       </c>
       <c r="G14" t="n">
         <v>1.5429</v>
@@ -1546,13 +1546,13 @@
         <v>2.9377</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5329</v>
+        <v>1.0735</v>
       </c>
       <c r="T14" t="n">
-        <v>2.716</v>
+        <v>0.874</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1831</v>
+        <v>0.1995</v>
       </c>
       <c r="V14" t="n">
         <v>0.6083</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2384</v>
+        <v>3.5785</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2857</v>
+        <v>0.4489</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9527</v>
+        <v>3.1296</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3224</v>
+        <v>2.397</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9735</v>
+        <v>0.9476</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3489</v>
+        <v>1.4494</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2401</v>
+        <v>2.8502</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9016</v>
+        <v>1.0122</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3385</v>
+        <v>1.838</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0822</v>
+        <v>-0.4532</v>
       </c>
       <c r="N15" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.0646</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0104</v>
+        <v>-0.3886</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1543</v>
+        <v>-2.9377</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7626</v>
+        <v>3.1336</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0324</v>
+        <v>0.7103</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9245</v>
+        <v>0.2611</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1078</v>
+        <v>0.4492</v>
       </c>
       <c r="V15" t="n">
         <v>0.2754</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9811</v>
+        <v>3.2851</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06279999999999999</v>
+        <v>1.1071</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0438</v>
+        <v>2.178</v>
       </c>
       <c r="G16" t="n">
-        <v>2.397</v>
+        <v>1.8982</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9476</v>
+        <v>3.0654</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4494</v>
+        <v>-1.1672</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8502</v>
+        <v>2.6857</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0122</v>
+        <v>3.1966</v>
       </c>
       <c r="L16" t="n">
-        <v>1.838</v>
+        <v>-0.5109</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4532</v>
+        <v>-0.7875</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0646</v>
+        <v>-0.1312</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3886</v>
+        <v>-0.6563</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1336</v>
+        <v>2.7419</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1129</v>
+        <v>0.6036</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2506</v>
+        <v>0.3799</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3634</v>
+        <v>0.2236</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1236</v>
+        <v>2.9922</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3775</v>
+        <v>0.8763</v>
       </c>
       <c r="F17" t="n">
-        <v>1.746</v>
+        <v>2.1159</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4821</v>
+        <v>2.3224</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6243</v>
+        <v>0.9735</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1064</v>
+        <v>1.3489</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9508</v>
+        <v>2.2401</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1225</v>
+        <v>0.9016</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8283</v>
+        <v>1.3385</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4687</v>
+        <v>0.0822</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7468</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2781</v>
+        <v>0.0104</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R17" t="n">
         <v>1.7626</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4749</v>
+        <v>0.7862</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.594</v>
+        <v>0.5152</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1192</v>
+        <v>0.271</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3329</v>
+        <v>0.2754</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7381</v>
+        <v>2.5864</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1861</v>
+        <v>0.7869</v>
       </c>
       <c r="F18" t="n">
-        <v>1.552</v>
+        <v>1.7995</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8982</v>
+        <v>1.4821</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0654</v>
+        <v>-0.6243</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1672</v>
+        <v>2.1064</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6857</v>
+        <v>1.9508</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1966</v>
+        <v>0.1225</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5109</v>
+        <v>1.8283</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7875</v>
+        <v>-0.4687</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1312</v>
+        <v>-0.7468</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6563</v>
+        <v>0.2781</v>
       </c>
       <c r="P18" t="n">
         <v>0.7834</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7419</v>
+        <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9434</v>
+        <v>-0.0121</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5411</v>
+        <v>-0.1847</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4023</v>
+        <v>0.1726</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5614</v>
+        <v>1.778</v>
       </c>
       <c r="E19" t="n">
         <v>1.3318</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2296</v>
+        <v>0.4462</v>
       </c>
       <c r="G19" t="n">
         <v>1.1162</v>
@@ -1936,13 +1936,13 @@
         <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0535</v>
+        <v>0.2701</v>
       </c>
       <c r="T19" t="n">
         <v>0.2135</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.16</v>
+        <v>0.0566</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8397</v>
+        <v>0.7015</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0398</v>
+        <v>0.1422</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.5593</v>
       </c>
       <c r="G20" t="n">
         <v>1.7981</v>
@@ -2014,13 +2014,13 @@
         <v>2.1543</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3919</v>
+        <v>0.2536</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0723</v>
+        <v>0.03</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4642</v>
+        <v>0.2236</v>
       </c>
       <c r="V20" t="n">
         <v>0.6083</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.632</v>
+        <v>-0.2897</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9454</v>
+        <v>-0.229</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6866</v>
+        <v>-0.0606</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0149</v>
@@ -2092,13 +2092,13 @@
         <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7299</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3805</v>
+        <v>0.3358</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3494</v>
+        <v>0.2766</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4332</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8824</v>
+        <v>-1.3604</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.771</v>
+        <v>-1.2952</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8885999999999999</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0906</v>
+        <v>-0.8864</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6761</v>
+        <v>-0.5631</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4145</v>
+        <v>-0.3233</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3635</v>
+        <v>0.2511</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8834</v>
+        <v>0.7264</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4802</v>
+        <v>-0.4753</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7271</v>
+        <v>-1.1375</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2073</v>
+        <v>-1.2895</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9344</v>
+        <v>0.152</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9585</v>
+        <v>-1.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>2.546</v>
+        <v>2.1543</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6195</v>
+        <v>0.0963</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6662</v>
+        <v>-0.0382</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0466</v>
+        <v>0.1345</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9988</v>
+        <v>-1.5495</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.1152</v>
+        <v>-0.3329</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8837</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2399</v>
+        <v>-2.4208</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0116</v>
+        <v>-3.692</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2284</v>
+        <v>1.2713</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8864</v>
+        <v>-3.0906</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5631</v>
+        <v>-1.6761</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3233</v>
+        <v>-1.4145</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2511</v>
+        <v>-2.3635</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7264</v>
+        <v>-1.8834</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4753</v>
+        <v>-0.4802</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1375</v>
+        <v>-0.7271</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2895</v>
+        <v>0.2073</v>
       </c>
       <c r="O23" t="n">
-        <v>0.152</v>
+        <v>-0.9344</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1751</v>
+        <v>-1.9585</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1543</v>
+        <v>2.546</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7832</v>
+        <v>1.0811</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7546</v>
+        <v>0.7452</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0286</v>
+        <v>0.336</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.5495</v>
+        <v>-0.9988</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3329</v>
+        <v>-0.1152</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2051</v>
+        <v>-3.1397</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8768</v>
+        <v>-1.0815</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3283</v>
+        <v>-2.0582</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2107</v>
@@ -2326,13 +2326,13 @@
         <v>1.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0056</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2664</v>
+        <v>0.0618</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2608</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2166</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.9489</v>
+        <v>13.6777</v>
       </c>
       <c r="E25" t="n">
-        <v>3.171399999999999</v>
+        <v>3.1716</v>
       </c>
       <c r="F25" t="n">
-        <v>7.777099999999999</v>
+        <v>10.5063</v>
       </c>
       <c r="G25" t="n">
-        <v>6.354299999999999</v>
+        <v>6.354299999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3437999999999999</v>
+        <v>0.3438000000000003</v>
       </c>
       <c r="I25" t="n">
         <v>6.0105</v>
@@ -2380,7 +2380,7 @@
         <v>15.6769</v>
       </c>
       <c r="K25" t="n">
-        <v>5.754700000000001</v>
+        <v>5.7547</v>
       </c>
       <c r="L25" t="n">
         <v>9.9222</v>
@@ -2389,13 +2389,13 @@
         <v>-9.322900000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.4109</v>
+        <v>-5.410900000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-3.9117</v>
       </c>
       <c r="P25" t="n">
-        <v>5.875299999999999</v>
+        <v>5.8753</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.6262</v>
@@ -2404,13 +2404,13 @@
         <v>23.5016</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8173</v>
+        <v>5.546</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1935</v>
+        <v>3.1936</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3762</v>
+        <v>2.3525</v>
       </c>
       <c r="V25" t="n">
         <v>-4.0978</v>
